--- a/KatalonData/EmailTextToPay/Manage_EmailText_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText_Prod.xlsx
@@ -1,36 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{D2C973B7-3E2E-4156-A615-D95CDE76E061}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D65C9CF-C65C-4F0D-94B9-A5BC7C85614B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="14" activeTab="15" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="ManageEmailTextSearch" r:id="rId1" sheetId="1"/>
-    <sheet name="ManageEmailTextFilter_FirstName" r:id="rId2" sheetId="2"/>
-    <sheet name="ManageEmailTextFilter_LastName" r:id="rId3" sheetId="6"/>
-    <sheet name="ManageEmailTextFilter_CompName" r:id="rId4" sheetId="7"/>
-    <sheet name="ManageEmailTextResend_FirstName" r:id="rId5" sheetId="3"/>
-    <sheet name="ManageEmailTextResend_LastName" r:id="rId6" sheetId="10"/>
-    <sheet name="ManageEmailTextResend_CompName" r:id="rId7" sheetId="11"/>
-    <sheet name="ManageEmailTextExpire_CompName" r:id="rId8" sheetId="13"/>
-    <sheet name="ManageEmailTextExpire_FirstName" r:id="rId9" sheetId="4"/>
-    <sheet name="ManageEmailTextExpire_LastName" r:id="rId10" sheetId="12"/>
-    <sheet name="ManageEmailTextCopy_FirstName" r:id="rId11" sheetId="5"/>
-    <sheet name="ManageEmailTextCopy_LastName" r:id="rId12" sheetId="14"/>
-    <sheet name="ManageEmailTextCopy_CompName" r:id="rId13" sheetId="15"/>
-    <sheet name="ManageEmailText_Errors_Search" r:id="rId14" sheetId="8"/>
-    <sheet name="ManageEmailText_Errors_NoSearch" r:id="rId15" sheetId="9"/>
-    <sheet name="ManageEmailTxtFilter_Par1stName" r:id="rId16" sheetId="16"/>
-    <sheet name="ManageEmailTxtFilter_ParLastNam" r:id="rId17" sheetId="17"/>
-    <sheet name="ManageEmailTxtFilter_ParCompNam" r:id="rId18" sheetId="18"/>
+    <sheet name="ManageEmailTextSearch" sheetId="1" r:id="rId1"/>
+    <sheet name="ManageEmailTextFilter_FirstName" sheetId="2" r:id="rId2"/>
+    <sheet name="ManageEmailTextFilter_LastName" sheetId="6" r:id="rId3"/>
+    <sheet name="ManageEmailTextFilter_CompName" sheetId="7" r:id="rId4"/>
+    <sheet name="ManageEmailTextResend_FirstName" sheetId="3" r:id="rId5"/>
+    <sheet name="ManageEmailTextResend_LastName" sheetId="10" r:id="rId6"/>
+    <sheet name="ManageEmailTextResend_CompName" sheetId="11" r:id="rId7"/>
+    <sheet name="ManageEmailTextExpire_CompName" sheetId="13" r:id="rId8"/>
+    <sheet name="ManageEmailTextExpire_FirstName" sheetId="4" r:id="rId9"/>
+    <sheet name="ManageEmailTextExpire_LastName" sheetId="12" r:id="rId10"/>
+    <sheet name="ManageEmailTextCopy_FirstName" sheetId="5" r:id="rId11"/>
+    <sheet name="ManageEmailTextCopy_LastName" sheetId="14" r:id="rId12"/>
+    <sheet name="ManageEmailTextCopy_CompName" sheetId="15" r:id="rId13"/>
+    <sheet name="ManageEmailText_Errors_Search" sheetId="8" r:id="rId14"/>
+    <sheet name="ManageEmailText_Errors_NoSearch" sheetId="9" r:id="rId15"/>
+    <sheet name="ManageEmailTxtFilter_Par1stName" sheetId="16" r:id="rId16"/>
+    <sheet name="ManageEmailTxtFilter_ParLastNam" sheetId="17" r:id="rId17"/>
+    <sheet name="ManageEmailTxtFilter_ParCompNam" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="129">
   <si>
     <t>Result</t>
   </si>
@@ -304,96 +304,6 @@
     <t>Search + verify success message</t>
   </si>
   <si>
-    <t>Change Me</t>
-  </si>
-  <si>
-    <t>Fri Jun 26 22:30:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:04:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:10:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:21:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:26:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:33:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:40:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:43:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:47:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:51:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 23:55:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:01:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:06:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:07:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:08:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:09:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:10:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:11:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:12:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:12:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:13:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:16:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:17:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:18:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:18:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:19:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:20:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:20:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 00:21:39 IST 2026</t>
-  </si>
-  <si>
     <t>Tue Jun 30 00:26:33 IST 2026</t>
   </si>
   <si>
@@ -403,22 +313,217 @@
     <t>Tue Jun 30 00:34:59 IST 2026</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 16:39:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 16:41:04 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Tue Jun 30 20:02:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 30 20:02:38 IST 2026</t>
+    <t>BBP Parking Fees GovTest</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 18:21:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 18:21:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 18:36:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 18:54:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 18:59:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 19:05:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 19:11:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 19:15:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 19:18:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 19:22:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 19:27:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 19:31:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 19:36:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 20:33:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:14:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:15:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:16:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:17:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:18:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:19:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:19:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:20:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:21:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:27:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:28:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:29:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:29:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:30:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:31:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:32:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:32:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:37:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:44:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 21:47:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:11:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:13:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:14:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:15:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:16:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:16:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:17:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:18:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:18:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:19:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:20:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:20:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:21:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:22:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:22:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:23:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:23:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:24:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:25:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:26:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:26:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:28:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:29:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:30:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:32:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:32:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:33:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:34:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:35:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:36:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:37:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:38:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:39:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:40:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:41:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:41:49 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -517,88 +622,88 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="27">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="4" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="4" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
-    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="4" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -615,10 +720,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -653,7 +758,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -705,7 +810,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -816,21 +921,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -847,7 +952,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -919,26 +1024,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="19" width="6.26953125" collapsed="true"/>
     <col min="2" max="2" customWidth="true" style="26" width="14.81640625" collapsed="true"/>
     <col min="3" max="3" customWidth="true" style="24" width="34.54296875" collapsed="true"/>
     <col min="4" max="4" customWidth="true" style="19" width="8.08984375" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="19" width="13.54296875" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="19" width="25.1796875" collapsed="true"/>
     <col min="6" max="16384" style="19" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -955,12 +1060,12 @@
         <v>5</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" t="s">
-        <v>92</v>
+    <row r="2" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>127</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>54</v>
@@ -969,15 +1074,15 @@
         <v>3</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row ht="13" r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" t="s">
-        <v>93</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>54</v>
@@ -986,7 +1091,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1003,13 +1108,13 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB20ABE5-EB40-4301-BBE4-8B897354D04D}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB20ABE5-EB40-4301-BBE4-8B897354D04D}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
@@ -1018,7 +1123,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="37.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1038,12 +1143,12 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>116</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -1052,20 +1157,20 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03671AC8-56DE-457F-802A-D25D162F1818}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03671AC8-56DE-457F-802A-D25D162F1818}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
@@ -1074,7 +1179,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="38.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1094,12 +1199,12 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="150" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>94</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1108,20 +1213,20 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8D7B23-96A3-4C14-84F1-69CBEB776D28}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8D7B23-96A3-4C14-84F1-69CBEB776D28}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
@@ -1130,7 +1235,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="38.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1150,12 +1255,12 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="150" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>96</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1164,20 +1269,20 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEFB455-878E-4283-8CDF-5280F5D2D976}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEFB455-878E-4283-8CDF-5280F5D2D976}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
@@ -1186,7 +1291,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="38.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1206,12 +1311,12 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="150" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>93</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1220,20 +1325,20 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC7F82F-C603-4F07-8548-EF17D188B148}">
-  <dimension ref="A1:H12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC7F82F-C603-4F07-8548-EF17D188B148}">
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
@@ -1246,7 +1351,7 @@
     <col min="8" max="16384" style="1" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1269,12 +1374,12 @@
         <v>35</v>
       </c>
     </row>
-    <row customHeight="1" ht="51.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
+    <row r="2" spans="1:7" ht="51.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>32</v>
@@ -1286,16 +1391,16 @@
         <v>16</v>
       </c>
     </row>
-    <row customHeight="1" ht="18.5" r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="18.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="4"/>
       <c r="E3" s="5"/>
     </row>
-    <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
+    <row r="4" spans="1:7" ht="62.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>33</v>
@@ -1304,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>34</v>
@@ -1313,16 +1418,16 @@
         <v>24</v>
       </c>
     </row>
-    <row ht="13" r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.25">
       <c r="C5" s="4"/>
       <c r="E5" s="5"/>
     </row>
-    <row ht="75" r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
+    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -1331,7 +1436,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F6" s="6">
         <v>59686725</v>
@@ -1340,12 +1445,12 @@
         <v>24</v>
       </c>
     </row>
-    <row ht="62.5" r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
+    <row r="7" spans="1:7" ht="62.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -1354,7 +1459,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>25</v>
@@ -1363,12 +1468,12 @@
         <v>24</v>
       </c>
     </row>
-    <row ht="75" r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
+    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>30</v>
@@ -1377,7 +1482,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -1386,12 +1491,12 @@
         <v>24</v>
       </c>
     </row>
-    <row ht="75" r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
+    <row r="9" spans="1:7" ht="75" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>31</v>
@@ -1400,7 +1505,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>27</v>
@@ -1409,12 +1514,12 @@
         <v>24</v>
       </c>
     </row>
-    <row ht="62.5" r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
+    <row r="10" spans="1:7" ht="62.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>43</v>
@@ -1423,7 +1528,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>42</v>
@@ -1432,12 +1537,12 @@
         <v>24</v>
       </c>
     </row>
-    <row ht="62.5" r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
+    <row r="11" spans="1:7" ht="62.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>44</v>
@@ -1446,7 +1551,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>46</v>
@@ -1455,12 +1560,12 @@
         <v>24</v>
       </c>
     </row>
-    <row ht="62.5" r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
+    <row r="12" spans="1:7" ht="62.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>45</v>
@@ -1469,7 +1574,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>47</v>
@@ -1479,13 +1584,13 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E26A7E4-F23A-4B0C-8BC6-AFD45C94E0CE}">
-  <dimension ref="A1:H13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E26A7E4-F23A-4B0C-8BC6-AFD45C94E0CE}">
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
@@ -1498,7 +1603,7 @@
     <col min="8" max="16384" style="1" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1521,12 +1626,12 @@
         <v>35</v>
       </c>
     </row>
-    <row ht="62.5" r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>77</v>
+    <row r="2" spans="1:7" ht="62.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>36</v>
@@ -1535,24 +1640,24 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="13" x14ac:dyDescent="0.25">
       <c r="C3" s="4"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
+    <row r="4" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>39</v>
@@ -1567,12 +1672,12 @@
         <v>37</v>
       </c>
     </row>
-    <row ht="62.5" r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
+    <row r="5" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>40</v>
@@ -1587,12 +1692,12 @@
         <v>37</v>
       </c>
     </row>
-    <row ht="62.5" r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
+    <row r="6" spans="1:7" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>41</v>
@@ -1610,12 +1715,12 @@
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C7" s="4"/>
     </row>
-    <row customHeight="1" ht="55" r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
+    <row r="8" spans="1:7" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>21</v>
@@ -1624,7 +1729,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>18</v>
@@ -1633,12 +1738,12 @@
         <v>37</v>
       </c>
     </row>
-    <row customHeight="1" ht="55" r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
+    <row r="9" spans="1:7" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>22</v>
@@ -1647,7 +1752,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>19</v>
@@ -1656,12 +1761,12 @@
         <v>37</v>
       </c>
     </row>
-    <row customHeight="1" ht="55" r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>83</v>
+    <row r="10" spans="1:7" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>23</v>
@@ -1670,7 +1775,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>20</v>
@@ -1679,16 +1784,16 @@
         <v>37</v>
       </c>
     </row>
-    <row ht="13" r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="13" x14ac:dyDescent="0.25">
       <c r="C11" s="4"/>
       <c r="E11" s="5"/>
     </row>
-    <row ht="50" r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
+    <row r="12" spans="1:7" ht="50" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>38</v>
@@ -1701,18 +1806,18 @@
         <v>37</v>
       </c>
     </row>
-    <row ht="13" r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="13" x14ac:dyDescent="0.25">
       <c r="C13" s="4"/>
       <c r="E13" s="5"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B68FE70-BD03-498B-B600-6B4B7C132BA1}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B68FE70-BD03-498B-B600-6B4B7C132BA1}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -1741,7 +1846,7 @@
     <col min="28" max="16384" style="16" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1761,35 +1866,35 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>85</v>
+    <row r="2" spans="1:6" s="13" customFormat="1" ht="38" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>121</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EABB53-51F5-4A90-B8E2-ADBC54583C91}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EABB53-51F5-4A90-B8E2-ADBC54583C91}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -1818,7 +1923,7 @@
     <col min="28" max="16384" style="16" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1838,35 +1943,35 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
+    <row r="2" spans="1:6" s="13" customFormat="1" ht="38" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD67883-E46D-4766-8983-E96E92BD2427}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD67883-E46D-4766-8983-E96E92BD2427}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -1895,7 +2000,7 @@
     <col min="28" max="16384" style="16" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1915,35 +2020,35 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>87</v>
+    <row r="2" spans="1:6" s="13" customFormat="1" ht="38" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="16" width="7.26953125" collapsed="true"/>
@@ -1972,7 +2077,7 @@
     <col min="28" max="16384" style="16" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1992,35 +2097,35 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="25.5" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
+    <row r="2" spans="1:6" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>118</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBD4D3F-6789-4F69-A50C-D0C16059C617}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBD4D3F-6789-4F69-A50C-D0C16059C617}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -2049,7 +2154,7 @@
     <col min="28" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2069,35 +2174,35 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>57</v>
+    <row r="2" spans="1:6" s="13" customFormat="1" ht="38" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D6A91F-B4A5-4069-ABF9-05ADE24D338D}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D6A91F-B4A5-4069-ABF9-05ADE24D338D}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -2126,7 +2231,7 @@
     <col min="28" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2146,35 +2251,35 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="38" r="2" s="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
+    <row r="2" spans="1:6" s="13" customFormat="1" ht="38" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD9BFD0-F930-4BCA-9C93-2C0B0F9DCF4B}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD9BFD0-F930-4BCA-9C93-2C0B0F9DCF4B}">
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
@@ -2183,7 +2288,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="47.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2203,12 +2308,12 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>125</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>13</v>
@@ -2217,15 +2322,15 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="19" r="3" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3"/>
-      <c r="B3"/>
+    <row r="3" spans="1:6" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
       <c r="C3" s="7"/>
       <c r="D3" s="1"/>
       <c r="E3" s="5"/>
@@ -2237,13 +2342,13 @@
       <c r="C5" s="7"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D613A990-B35A-40B9-8717-E014B2376EAA}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D613A990-B35A-40B9-8717-E014B2376EAA}">
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
@@ -2252,7 +2357,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="47.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2272,12 +2377,12 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>126</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>51</v>
@@ -2286,15 +2391,15 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="19" r="3" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3"/>
-      <c r="B3"/>
+    <row r="3" spans="1:6" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
       <c r="C3" s="7"/>
       <c r="D3" s="1"/>
       <c r="E3" s="5"/>
@@ -2306,13 +2411,13 @@
       <c r="C5" s="7"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C48FAA-06E6-4269-9430-6E787AF33FF2}">
-  <dimension ref="A1:G10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C48FAA-06E6-4269-9430-6E787AF33FF2}">
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
@@ -2321,7 +2426,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="47.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2341,12 +2446,12 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>123</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>52</v>
@@ -2355,7 +2460,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>7</v>
@@ -2371,13 +2476,13 @@
       <c r="F10" s="19"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B02ABF-6BE7-42F8-924B-66A45432828E}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B02ABF-6BE7-42F8-924B-66A45432828E}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
@@ -2386,7 +2491,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="37.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2406,12 +2511,12 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>114</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -2420,20 +2525,20 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CBCA1D-16A9-43B0-BA4E-60CC8E0C88C7}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CBCA1D-16A9-43B0-BA4E-60CC8E0C88C7}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
@@ -2442,7 +2547,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="37.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2462,12 +2567,12 @@
         <v>6</v>
       </c>
     </row>
-    <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>115</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -2476,13 +2581,13 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>